--- a/core/src/main/resources/baseFiles/excel/RawXL/Sheet.xlsx
+++ b/core/src/main/resources/baseFiles/excel/RawXL/Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="14440"/>
+    <workbookView windowWidth="23340" windowHeight="11980"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1211,40 +1211,50 @@
   <sheetPr/>
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="3" max="3" width="12.6875"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:J452">
+    <sortCondition ref="D2:D452"/>
+    <sortCondition ref="J2:J452"/>
+    <sortCondition ref="I2:I452"/>
+    <sortCondition ref="F2:F452"/>
+    <sortCondition ref="C2:C452"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
